--- a/review/etnografiya/may-december/may-december.xlsx
+++ b/review/etnografiya/may-december/may-december.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда гость переступает порог двора?</t>
+          <t xml:space="preserve">Гость и хозяин проходят одну калитку, но идут разными путями. Маленькая граница двора открывает порядок соседства и домашнего труда.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -140,7 +140,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему сани нельзя просто поставить на колёса?</t>
+          <t xml:space="preserve">Телега отличается от саней не только колёсами. Летний путь требует другой опоры и размещения груза — устройство меняется вместе с дорогой.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -167,7 +167,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что первым замечаешь в мужской рубахе?</t>
+          <t xml:space="preserve">Застёжка косоворотки смещена в сторону. Небольшая деталь сразу меняет вид рубахи и помогает различить крой, не придумывая единую историю его появления.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -194,7 +194,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как поднять руки в рубахе из прямых полотнищ?</t>
+          <t xml:space="preserve">Небольшой лоскут под рукавом даёт свободу движения. Ластовица показывает, как точная деталь меняет удобство рубахи из прямых полотнищ.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что нужно взять человеку, который уйдёт со стадом на весь день?</t>
+          <t xml:space="preserve">Пастух уходит со стадом на целый день. Его сумка собирает нужное вдали от дома — каждый предмет занимает место ради конкретного дела.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -248,7 +248,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало выпаса становилось событием для деревни?</t>
+          <t xml:space="preserve">Первый выход стада становится событием деревни. В обычаях Егорьева дня сезонный труд соединяется с заботой людей о благополучии хозяйства.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -275,7 +275,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли услышать, где пасётся твоя корова?</t>
+          <t xml:space="preserve">Корова скрылась из виду, но ботало выдаёт её движение. Маленькая звучащая вещь помогает человеку следить за стадом на расстоянии.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -302,7 +302,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как двор помогает заботиться о домашних птицах?</t>
+          <t xml:space="preserve">Для птицы во дворе отводят гнездо, корм и воду. Небольшой участок хозяйства показывает, сколько ежедневного внимания требует домашняя живность.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -329,7 +329,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие следы большого события остаются в домашнем альбоме?</t>
+          <t xml:space="preserve">Большая Победа остаётся в семейном альбоме. Снимок сохраняет лица, а подписи и воспоминания возвращают имена людей и обстоятельства встречи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -356,7 +356,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как прямоугольные полотнища становятся просторной одеждой?</t>
+          <t xml:space="preserve">Прямоугольные полотнища собираются в просторный сарафан. Объём рождается из сборки ткани — сложный силуэт начинается с простых частей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -383,7 +383,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли расширить подол, сохранив узкий верх?</t>
+          <t xml:space="preserve">Клинья расширяют подол, оставляя верх узким. В косоклинном сарафане мастерство кроя видно по тому, как распределяется ткань в движении.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -410,7 +410,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как многослойность меняет весь костюм?</t>
+          <t xml:space="preserve">Короткая душегрея меняет вид длинного сарафана. Костюм складывается слоями: одна вещь задаёт новый силуэт всему наряду.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -437,7 +437,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочая вещь могла стать нарядной?</t>
+          <t xml:space="preserve">Передник защищает одежду и несёт отделку. Рабочая вещь может стать нарядной — местная традиция соединяет пользу с вниманием к красоте.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая деталь меняет причёску?</t>
+          <t xml:space="preserve">Косник держится на конце девичьей косы. Маленькое украшение рассчитано на конкретное место: крепление объясняет форму не хуже узора.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что скрывается за одним названием?</t>
+          <t xml:space="preserve">За названием «сорока» скрывается убор из нескольких частей. Каждый слой делает свою работу, прежде чем появится знакомый нарядный силуэт.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему украшение интересно рассматривать не только спереди?</t>
+          <t xml:space="preserve">Подвесы нагрудного украшения видны сбоку и в движении. Наряд устроен объёмно: способ крепления хранит часть мастерского замысла.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как покупной материал меняет привычную рубаху?</t>
+          <t xml:space="preserve">Покупной кумач входит в деревенскую одежду. Новый материал меняет поверхность привычной рубахи, сохраняя связь обновления с местным костюмом.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая ткань выдавала стремление одеться модно?</t>
+          <t xml:space="preserve">Плис придаёт нарядным штанам особую поверхность. Молодёжная мода читается в фактуре ткани, которую трудно заметить издали.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">В какой момент городской силуэт становится деревенским?</t>
+          <t xml:space="preserve">Кофта и юбка составляют «парочку». Новый силуэт входит в местный гардероб — история деревенской одежды продолжается через перемены кроя.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли один платок выглядеть как три разные вещи?</t>
+          <t xml:space="preserve">Один квадратный платок можно сложить и надеть по-разному. Движение рук меняет силуэт вещи без единого нового шва.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему этот день нельзя навсегда поставить на 21 мая?</t>
+          <t xml:space="preserve">Вознесение зависит от даты Пасхи и не закреплено за одним числом мая. Подвижный праздник показывает другой способ устроить годовой круг.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна память соединяла разные занятия людей?</t>
+          <t xml:space="preserve">Никола вешний входит в хозяйственный календарь разных мест. Один праздничный день связывает церковную память с конкретными занятиями людей.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает подошва о работе мастера?</t>
+          <t xml:space="preserve">Подошва прячет работу сапожника от первого взгляда. Гвозди и швы показывают, каким способом мастер удержал вместе части обуви.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как научиться читать, если книг совсем немного?</t>
+          <t xml:space="preserve">Домашняя азбука превращает буквы в освоенное умение. Одна страница хранит путь от узнавания знака к слову, которое ребёнок читает сам.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли понять работу замка, не сломав его?</t>
+          <t xml:space="preserve">Поворот ключа двигает скрытый запор. Медный замок соединяет небольшое движение руки с защитой вещей, которым хозяин отвёл особое место.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что держит створку годами?</t>
+          <t xml:space="preserve">Тяжёлая дверь держится на кованых петлях. Длинная металлическая полоса распределяет крепление — кузнечная работа остаётся в ежедневном движении створки.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая скамья становится местом общения?</t>
+          <t xml:space="preserve">Лавка у дома собирает соседей. Простая скамья становится местом обмена новостями, когда люди задерживаются рядом и обращаются друг к другу.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему берёза появляется в рассказах о начале лета?</t>
+          <t xml:space="preserve">Берёзовые ветви входят в семицкий обряд. Зелёный материал становится частью праздничного действия, порядок которого различается от места к месту.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько изгибов превращаются в бегущую лошадь?</t>
+          <t xml:space="preserve">Несколько изгибов кисти создают городецкого коня. Движение животного читается в силуэте ещё до появления мелких деталей нарядной росписи.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли продолжить узор, не зная его названия?</t>
+          <t xml:space="preserve">Красный и чёрный складываются в повторяющийся ряд. Мезенская роспись держит ритм узора: следующий элемент связан с уже написанными.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в знакомом интерьере в праздничный день?</t>
+          <t xml:space="preserve">На Троицу привычный дом получает зелёное убранство. Местный обычай делает праздник видимым внутри повседневного семейного пространства.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли сделать упругую игрушку без резины?</t>
+          <t xml:space="preserve">Тряпичный мяч обходится без резины. Домашние материалы собираются в игрушку — игра начинается с умения придать форму тому, что под рукой.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном календаре могли откладывать работу с землёй?</t>
+          <t xml:space="preserve">В народном представлении земля бывает именинницей. Отложенная работа в Духов день показывает обрядовую паузу внутри непрерывного сельского труда.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как июньский посев связан с зимней рубахой?</t>
+          <t xml:space="preserve">Имя Олёны-льняницы связывает посев с будущим полотном. Между летним полем и зимней рубахой лежит длинная цепь человеческой работы.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее в этой игре — скорость или внимание?</t>
+          <t xml:space="preserve">В горелках пара разбегается, а водящему надо успеть отреагировать. Скорость работает вместе с вниманием к моменту начала движения.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда выгоднее бежать, а когда ждать?</t>
+          <t xml:space="preserve">В лапте удар открывает время для перебежки. Игрок соотносит свой старт с действиями соперников — командная игра требует общего расчёта.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна и та же пятёрка создаёт разные задачи?</t>
+          <t xml:space="preserve">Пять чурок складываются в разные фигуры городков. Материал остаётся прежним, но новое расположение меняет задачу для каждого броска.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем участники заранее договариваются о границах?</t>
+          <t xml:space="preserve">Граница площадки меняет игру в салочки. Договорённость участников становится действующим правилом, без которого один и тот же бег означает разное.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ритм помогает группе принять решение?</t>
+          <t xml:space="preserve">Считалка распределяет слоги между участниками и выбирает водящего. Ритм помогает группе начать игру с общего принятого порядка.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли игрушка сохранить подробности взрослого наряда?</t>
+          <t xml:space="preserve">Наряд самодельной куклы умещается в ладони. Игрушка способна сохранить детали взрослого местного костюма в масштабе детской игры.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать момент для движения?</t>
+          <t xml:space="preserve">В Тимоне движение ног связано с наигрышем. Музыкальная опора становится телесным ритмом — услышанное продолжается в шаге танцующего.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как участники сохраняют общее движение?</t>
+          <t xml:space="preserve">Карагод держится на согласованном движении людей. Общий круг складывается из отдельных шагов, которые участники соотносят друг с другом.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто ведёт, а кто отвечает?</t>
+          <t xml:space="preserve">Инструменты плясового ансамбля вступают в разное время. В общем звучании слышны ведущие и ответные движения музыкальной фразы.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли рабочее дело иметь свой напев?</t>
+          <t xml:space="preserve">В Фощеватове песня сопровождает полотьё. Напев сохраняет связь с конкретным сезонным делом, а не только с праздничным выступлением.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему соседние песни звучат так по-разному?</t>
+          <t xml:space="preserve">В одном селе Лопатни живут песни разных слоёв репертуара. Соседство старого и нового показывает традицию, которая продолжает меняться.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается строка, если мелодия ещё продолжается?</t>
+          <t xml:space="preserve">В песнях Осереди слово может закончиться раньше распева. Длинная музыкальная фраза раскрывает время, которое голос даёт одной строке.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ворот меняет усилие человека?</t>
+          <t xml:space="preserve">Рукоять колодезного ворота поднимает ведро из глубины. Поворот руки превращается в вертикальное движение тяжёлого запаса воды.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как распределить небольшой участок между разными культурами?</t>
+          <t xml:space="preserve">Огород рядом с домом делят между разными культурами. За небольшими грядами стоит сезонный порядок ухода и будущего семейного стола.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старый рассказ о репке понятен через хозяйство?</t>
+          <t xml:space="preserve">Репа возвращает знакомую сказку в хозяйственный мир. За большой сказочной работой стоит настоящий овощ и его место в домашней еде.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что в летней еде нельзя повторить зимой без запасов?</t>
+          <t xml:space="preserve">Сезонная зелень меняет состав обеда. Щавель показывает, как стол связан с появлением свежих растений, а не только с зимним запасом.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что видно над водой и что происходит под ней?</t>
+          <t xml:space="preserve">Поплавок остаётся на поверхности и передаёт движение снасти. Маленькая вещь делает видимым то, что происходит под водой.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему названия дней хранят внимание к погоде?</t>
+          <t xml:space="preserve">Народный календарь сохраняет наблюдения за летней погодой. Имя Фёдора Стратилата становится точкой сезонной памяти, а не гарантией прогноза.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плетёная ловушка удерживает добычу?</t>
+          <t xml:space="preserve">У мережи вход устроен иначе, чем выход. Форма рыболовной снасти направляет движение — результат зависит от конструкции целого предмета.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем лодочнику сосуд, которым ничего не пьют?</t>
+          <t xml:space="preserve">Черпак убирает воду со дна лодки. Простая ручная вещь напоминает, что работа на воде включает постоянную заботу о самом судне.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая часть узора одновременно решает бытовую задачу?</t>
+          <t xml:space="preserve">Наличник украшает окно и закрывает стык. Красота резной детали соединена с устройством дома: узор занимает место конкретной строительной части.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется дом, когда ставни закрывают?</t>
+          <t xml:space="preserve">Ставни дают окну дополнительное закрытие. Створки меняют вид фасада и повседневное обращение с границей между комнатой и улицей.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить гречиху от привычного хлебного колоса?</t>
+          <t xml:space="preserve">Гречиха вошла в народное имя Акулинина дня. Календарное название связывает растение с сезонным вниманием людей к будущему урожаю.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему крупа не похожа на длинное зерно ржи?</t>
+          <t xml:space="preserve">У гречневого зерна характерная трёхгранная форма. Знакомая крупа возвращает взгляд от тарелки к растению и обработке урожая.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как цветы удерживают композицию на круглом подносе?</t>
+          <t xml:space="preserve">Листья жостовской росписи собираются веерными движениями кисти. Растительный мотив держится на порядке мазков, а не на обводке готового контура.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как узнать игрушку ещё до раскраски?</t>
+          <t xml:space="preserve">Филимоновская свистулька вытягивает силуэт в глине. Местный почерк виден ещё до росписи — форму и звучание мастер создаёт вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что человек выбирает рассказать близким прежде всего?</t>
+          <t xml:space="preserve">Летние новости укладываются на одном листе. Домашнее письмо сохраняет личный голос человека, которому предстояло преодолеть расстояние словами.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему не всякой косой работают одинаково?</t>
+          <t xml:space="preserve">Изгиб косы-горбуши подсказывает движение косаря. Форма инструмента связана с работой тела, а не только с остротой металлического края.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, если рукоять слишком длинна?</t>
+          <t xml:space="preserve">Косовище подгоняют под человека. Деревянная рукоять соединяет рост, хват и движение — удобство рождается из точного соответствия работнику.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему работа в поле прерывается короткими остановками?</t>
+          <t xml:space="preserve">Брусок возвращает косе рабочую остроту. Покос требует заботы об инструменте: остановка для правки становится частью непрерывного труда.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как устроить жизнь, когда рабочее место далеко от дома?</t>
+          <t xml:space="preserve">На долгий покос берут больше одной косы. Еда, одежда и рабочие вещи собирают повседневную жизнь там, где семье предстоит провести несколько дней.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему скошенную траву не сразу уносят под крышу?</t>
+          <t xml:space="preserve">Скошенная трава ещё не стала зимним запасом. Просушка требует времени и внимания — поспешность может перечеркнуть тяжёлую работу покоса.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у летнего дня такое имя?</t>
+          <t xml:space="preserve">Банный обычай входит в день Аграфены Купальницы. Подготовка тела и домашние действия соединяются с местным порядком летнего праздника.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить народное предание от свойства растения?</t>
+          <t xml:space="preserve">Купальский рассказ обещает чудесный цветок. Предание открывает народное воображение и ожидание необычного, сохраняя отличие от ботанического факта.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли разобраться в большой семье по одному рассказу?</t>
+          <t xml:space="preserve">За семейным столом видна сеть родства. Один человек оказывается для соседей сыном, супругом или дядей — связь зависит от точки отсчёта.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить много лёгкого, но объёмного груза?</t>
+          <t xml:space="preserve">Сено хранят над хозяйственным двором. Запас занимает верхний ярус дома и связывает устройство постройки с годовым ритмом ухода за животными.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько людей работают без одинаковых заданий?</t>
+          <t xml:space="preserve">Артель делит большое дело между людьми. Общий результат складывается из разных ролей, согласованности действий и принятого порядка работы.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как накормить семью, когда все далеко от печи?</t>
+          <t xml:space="preserve">Полевой обед должен добраться до работников. Сосуды и переноска становятся частью питания — домашняя еда получает собственный маршрут.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает праздник и начало сенокоса в Кижах?</t>
+          <t xml:space="preserve">Петров день отмечает перемену летнего хозяйственного ритма. Праздник включён в местный год работ, который не сводится к одной общей схеме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему два сильных гребца могут мешать друг другу?</t>
+          <t xml:space="preserve">Два весла должны работать согласованно. Направление лодки зависит от соотношения движений — совместное усилие требует общего ритма.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может служить якорем без сложной металлической формы?</t>
+          <t xml:space="preserve">Тяжёлый камень удерживает лодку через привязанную снасть. Природный материал получает новое назначение в продуманном рыбацком устройстве.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь из села становится музейным свидетельством?</t>
+          <t xml:space="preserve">Коллекция Ольги Семёновой начинается со встреч с людьми и вещами. За музейным собранием стоит личная работа узнавания и сохранения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название вещи без места и имени почти бесполезно?</t>
+          <t xml:space="preserve">Полевой блокнот удерживает то, что легко забыть после встречи. Имя, место и обстоятельства записи помогают вещи сохранить человеческий контекст.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как восстановить одну ячейку, не переделывая всё полотно?</t>
+          <t xml:space="preserve">Рыбацкая игла проводит нить через ячейки сети. Починка возвращает снасти рабочую форму — добыча начинается с терпеливого ручного ремонта.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как переносная ёмкость связана со средой рыбака?</t>
+          <t xml:space="preserve">Садок оставляет пойманную рыбу в воде. Устройство продолжает работу рыбака после ловли, удерживая улов в отдельном пространстве.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у человека рядом с ульем появляется дым?</t>
+          <t xml:space="preserve">Дымарь входит в набор пасечника. Форма прибора и направленный выход дыма показывают, как инструмент подчинён конкретной работе с ульем.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как природная форма превращается в хозяйственную вещь?</t>
+          <t xml:space="preserve">Ствол дерева становится ульем-колодой. Человек использует природную форму, превращая её в часть устроенного пчелиного хозяйства.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда часть улья становится съёмной?</t>
+          <t xml:space="preserve">Рамку можно вынуть из улья отдельно. Съёмная деталь меняет доступ к внутреннему устройству — работа пасечника получает новую возможность.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как несколько слабых полос становятся одним креплением?</t>
+          <t xml:space="preserve">Тонкое лыко собирается в прочную верёвку. Скручивание связывает отдельные волокна: запас прочности рождается из их совместной работы.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где нужна ткань, которую не наденешь на праздник?</t>
+          <t xml:space="preserve">Грубая рогожа тоже требует ткацкого умения. Польза прочного полотна держится на порядке переплетения, даже когда вещь не называют нарядной.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему деревянная вещь выглядит металлической?</t>
+          <t xml:space="preserve">Хохломская ложка сияет золотым цветом, оставаясь деревянной. Отделка меняет вид материала — мастерство скрыто под знакомым праздничным блеском.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как кисть получает свет и тень без смены краски?</t>
+          <t xml:space="preserve">Один синий цвет даёт множество оттенков гжельского мазка. Нажим и движение кисти превращают ограниченную палитру в объёмный рисунок.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему узор легко узнать издалека?</t>
+          <t xml:space="preserve">Круги и полосы становятся нарядом дымковской барышни. Простой элемент работает вместе с формой фигурки и ритмом всей росписи.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто этот персонаж между человеком и конём?</t>
+          <t xml:space="preserve">Каргопольский Полкан соединяет необычные черты в глиняной фигуре. Местная игрушка хранит собственный образ героя, узнаваемый по силуэту.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему плоский рисунок иначе смотрится на объёме?</t>
+          <t xml:space="preserve">Цветок Полховского Майдана ложится на округлую поверхность. Роспись рассчитана на объём: рисунок продолжается за пределами одного взгляда.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сделать так, чтобы каждая фигура вошла в следующую?</t>
+          <t xml:space="preserve">Матрёшки должны войти одна в другую. Размер каждой фигурки связан с соседними — точность токарной работы удерживает расписную семью вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что гремит в игрушке, у которой ничего не видно?</t>
+          <t xml:space="preserve">Внутри берестяного шаркунка спрятан источник звука. Переплетённая оболочка превращает движение руки в слышимый ответ маленькой игрушки.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли найти ручную работу по двум похожим предметам?</t>
+          <t xml:space="preserve">Ручные вещи немного различаются даже в одном ряду. След инструмента и ладони сохраняет решения мастера, которые не повторяются совершенно одинаково.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему изогнутое лезвие удобно для выбранного движения?</t>
+          <t xml:space="preserve">Серп работает с горстью стеблей, удержанной рукой. Жатва складывается из множества повторённых движений — урожай собирают в человеческом масштабе.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарный день связывали с переменами погоды?</t>
+          <t xml:space="preserve">Ильин день входит в народный рассказ о перемене лета. Календарная память соединяет праздник с сезонными наблюдениями, не превращая их в прогноз.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как охапка стеблей превращается в удобный груз?</t>
+          <t xml:space="preserve">Сноп придаёт срезанным стеблям переносную форму. Урожай становится отдельной связкой, которую можно поднять, поставить и перевезти.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли связать стебли без покупной верёвки?</t>
+          <t xml:space="preserve">Перевясло делают из самого растительного материала. Часть урожая удерживает другую часть — простое крепление рождается прямо во время работы.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем наряд для работы отличается от праздничного?</t>
+          <t xml:space="preserve">Жнивная рубаха принадлежит тяжёлой поре полевых работ. Крой и материал помогают увидеть связь одежды с движением и сезонной нагрузкой.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто присматривает за младшими, пока взрослые жнут?</t>
+          <t xml:space="preserve">В семейной работе на поле было несколько ролей. Детское участие требует увидеть конкретное занятие, а не переносить взрослый труд на всех одинаково.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему завершение жатвы не всегда означает пустое поле?</t>
+          <t xml:space="preserve">Последние колосья могли оставлять для обрядового действия. Завершение жатвы получало местный смысл, который не сводится к уборке остатка урожая.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему орудие состоит из двух подвижных частей?</t>
+          <t xml:space="preserve">Цеп отделяет зерно ударами по снопам. Подвижное соединение деревянных частей превращает замах человека в работу другого конца орудия.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем снопы везут в особое место?</t>
+          <t xml:space="preserve">Ток — отдельная площадка для работы с урожаем. Расположение снопов и действий показывает, что обмолоту нужен организованный простор.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что делает отдельная постройка, чего не сделает жилая изба?</t>
+          <t xml:space="preserve">В овине снопы готовят к обмолоту. Урожай проходит дополнительный этап обработки, прежде чем зерно отделят от стеблей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как движение воздуха отделяет лёгкое от тяжёлого?</t>
+          <t xml:space="preserve">Воздух помогает отделить зерно от лёгких примесей. Веялка использует различие материала — невидимый поток становится рабочей силой.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему зерно нельзя просто высыпать где угодно?</t>
+          <t xml:space="preserve">В сусеке зерну отводят отдельное место. Домашний запас требует границ и порядка, чтобы результат одного сезона служил семье дальше.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что рассказывает увеличенная ячейка о собранном продукте?</t>
+          <t xml:space="preserve">Медовый сот приносит природную структуру в хозяйство человека. Пасечный труд начинается с внимания к тому, что создают сами пчёлы.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как хозяйственный запас входит в календарный обычай?</t>
+          <t xml:space="preserve">На Медовый Спас продукт пасеки становится праздничным даром. Работа с пчёлами входит в годовой круг встреч, угощения и благодарности.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся ценным после извлечения мёда?</t>
+          <t xml:space="preserve">Пасека даёт не только мёд, но и воск. Один хозяйственный мир снабжает человека разными материалами, каждому из которых находится своё применение.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плод становится зимним запасом?</t>
+          <t xml:space="preserve">Мочёные яблоки меняют вкус во время хранения. Заготовка превращает летний плод в другой опыт домашней еды, доступный после сбора урожая.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему после сушки меняются размер и способ хранения?</t>
+          <t xml:space="preserve">При сушке грибы становятся легче и занимают меньше места. Лесной сбор получает форму запаса — результат сохраняют отдельной домашней работой.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему для ягод важны форма и глубина корзины?</t>
+          <t xml:space="preserve">Ягодное лукошко должно донести хрупкий сбор. Плетёная форма рассчитана на содержимое: труд собирателя продолжается дорогой домой.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает яблоко, семейный стол и церковный календарь?</t>
+          <t xml:space="preserve">Яблочный Спас связывает плоды с праздничной историей. Сезонный урожай появляется в угощении и обычае конкретного местного сообщества.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Всегда ли кисель был сладким напитком?</t>
+          <t xml:space="preserve">Знакомое слово «кисель» хранит историю другого блюда. Сравнение старого и нового стола показывает, как название переживает перемены приготовления.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем готовая мука отличается от просто размолотого зерна?</t>
+          <t xml:space="preserve">Толокно — результат нескольких этапов подготовки зерна. За простой домашней пищей скрыто время работы, которого не видно в готовой порции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем рассматривать посуду сбоку, а не только спереди?</t>
+          <t xml:space="preserve">Просвет в кваснике делает сосуд узнаваемым. Необычная форма предлагает рассмотреть устройство бытовой вещи со всех сторон, а не только спереди.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как напиток переносили и разливали покупателям?</t>
+          <t xml:space="preserve">Сбитенник связан с горячим напитком и уличным угощением. Специальный сосуд выводит домашнее тепло в пространство городской встречи.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у одной семьи бывают разные правила трапезы?</t>
+          <t xml:space="preserve">Постный и скоромный стол различаются набором продуктов. Годовой календарь меняет повседневный выбор еды, не меняя саму потребность накормить семью.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как положить заготовку туда, куда рукой не достать?</t>
+          <t xml:space="preserve">Длинная хлебная лопата достигает глубины печи. Расстояние между руками и жаром превращено в размер простого деревянного инструмента.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему богатый запас всё равно делят?</t>
+          <t xml:space="preserve">Часть зерна оставляют для нового посева. Урожай одновременно кормит сегодня и сохраняет возможность следующего года — весь запас съесть нельзя.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему путь к ткани проходит через воду?</t>
+          <t xml:space="preserve">Лён меняется на мочиле ещё до прядения. Будущая нить начинается с обработки стебля, когда ткань пока невозможно увидеть в материале.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник соседствует с заботой об урожае?</t>
+          <t xml:space="preserve">Успение входит в народную память о завершении лета. Праздник встречается с хозяйственным сезоном, но местный порядок работ требует отдельного рассказа.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему один день называется разными дарами?</t>
+          <t xml:space="preserve">Ореховый, Хлебный и Холщовый — имена одного Спаса. Разные названия сохраняют несколько хозяйственных связей внутри общей праздничной даты.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Куда уходит стебель после обмолота?</t>
+          <t xml:space="preserve">Солома служит подстилкой после того, как зерно убрано. У урожая оказывается больше одной полезной части — хозяйство продолжает использовать растение.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочему животному посвящали особый день?</t>
+          <t xml:space="preserve">День Флора и Лавра связан с заботой о лошадях. Праздничное внимание обращено к животному, чья сила участвовала в ежедневном человеческом труде.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что ребёнок несёт из дома в школу?</t>
+          <t xml:space="preserve">Первый ранец собирает школьные вещи в дорожный набор. Учёба становится ежедневным выходом из дома — новый порядок жизни виден в одном предмете.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старая тетрадь хранит след нажима?</t>
+          <t xml:space="preserve">Перьевая ручка оставляет строку по движению руки. Нажим и направление становятся частью письма: инструмент требует освоенного телесного навыка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как повтор помогает обрести навык?</t>
+          <t xml:space="preserve">Одинаковые буквы в прописи готовят собственный почерк. Повторение даёт руке уверенность, прежде чем запись начнёт отличаться личным движением.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить написанное, не размазав его?</t>
+          <t xml:space="preserve">Промокательная бумага помогает ещё мокрой строке. Маленькая школьная принадлежность хранит способ письма, которому требовалось время на высыхание.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как посчитать покупку без записи столбиком?</t>
+          <t xml:space="preserve">На счётах число видно по положению косточек. Движение пальцев меняет запись и расчёт — абстрактное количество получает материальную форму.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему покупателю важно смотреть на гирю?</t>
+          <t xml:space="preserve">Клеймо на гире связано с доверием к мере. Маленький груз участвует в сделке, где покупателю и продавцу важно одинаково понимать вес.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одно противовесное устройство заменяет две чаши?</t>
+          <t xml:space="preserve">Безмен взвешивает груз на подвеске. Компактное устройство переводит тяжесть вещи в положение, по которому человек узнаёт меру.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему мерка должна быть понятна обеим сторонам?</t>
+          <t xml:space="preserve">Аршином отмеряют ткань для продажи. Будущий наряд начинается с длины полотна — привычная мера связывает торговлю с работой портного.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как найти нужное среди множества торговцев?</t>
+          <t xml:space="preserve">Ярмарочные покупки складываются в путь между рядами. Торговое пространство организует встречу разных нужд, товаров и человеческих занятий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие слова убеждали покупателя сто лет назад?</t>
+          <t xml:space="preserve">Товарная этикетка обещает качество до открытия упаковки. Надпись и рисунок показывают, как производитель обращается к незнакомому покупателю.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему красивую упаковку не спешат выбрасывать?</t>
+          <t xml:space="preserve">Жестяная коробка остаётся после покупки. Упаковка получает вторую домашнюю жизнь — её содержимое меняется, а след прежнего товара сохраняется.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как вещь помогает откладывать понемногу?</t>
+          <t xml:space="preserve">Копилка собирает небольшие суммы в общий запас. Отдельная монета становится частью будущего решения, которое ещё нельзя оплатить сегодня.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о семье по списку покупок?</t>
+          <t xml:space="preserve">Домашние расходы попадают в тетрадь. Запись делает хозяйство обозримым: деньги связываются с датами, покупками и памятью о сделанном выборе.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему начало осени могло напоминать новый год?</t>
+          <t xml:space="preserve">Семёнов день отмечают особым местным порядком. Встреча осени получает человеческую форму через действия, которые повторяются в годовом круге.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется распорядок, когда темнеет раньше?</t>
+          <t xml:space="preserve">Новая лучина даёт свет для вечерней работы. С наступлением длинных вечеров домашнее ремесло зависит от маленького, постоянно сменяемого огня.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему продукты отправляют вниз?</t>
+          <t xml:space="preserve">Погреб использует прохладу как часть домашнего устройства. Место хранения помогает урожаю пережить сезон, когда свежий сбор уже закончился.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем большой семье большая ёмкость?</t>
+          <t xml:space="preserve">Капустный запас укладывают в кадку слоями. Большая ёмкость собирает множество малых действий — за зимней порцией стоит общая работа заготовки.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонный инструмент похож на маленький полумесяц?</t>
+          <t xml:space="preserve">Сечка рубит капусту особым лезвием. Назначение инструмента видно в его движении: знакомый продукт требует собственной организации работы.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему хлебный день начинается задолго до печи?</t>
+          <t xml:space="preserve">В квашне тесто оставляют подниматься. Хлеб требует не только движения рук, но и ожидания — домашний труд умеет вовремя остановиться.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сезонная еда остаётся на столе позже?</t>
+          <t xml:space="preserve">Солёные огурцы переносят летний огород в холодный сезон. Заготовка меняет вкус продукта и продлевает путь урожая до семейного стола.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что связывает украшение и знакомый хозяйственный образ?</t>
+          <t xml:space="preserve">Коромысельные серьги напоминают знакомое орудие формой. Бытовое сравнение помогает прочитать устройство украшения, которое носили совсем иначе.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как небольшая вещь становится личной?</t>
+          <t xml:space="preserve">Лента и накосник входят в причёску как подарок. Личная вещь соединяет украшение волос с памятью о человеке, который её преподнёс.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее — вместительность или содержимое?</t>
+          <t xml:space="preserve">Сундук невесты собирает вещи, подготовленные к новой жизни. За наполнением стоит запас семейного труда, который нельзя измерить одним размером сундука.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семья показывала подготовку к свадьбе?</t>
+          <t xml:space="preserve">Приданое выставляют на обозрение. Ткань, швы и отделка делают мастерство видимым другим людям — домашний труд получает общественную оценку.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как временный заработок меняет домашний календарь?</t>
+          <t xml:space="preserve">Осенний наём выводит работника за пределы деревни. Дорога связывает семейное хозяйство с чужой работой и новым порядком повседневной жизни.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие детали портрета были специально подготовлены?</t>
+          <t xml:space="preserve">В фотоателье человек выбирает, как предстать перед камерой. Костюм, поза и обстановка превращают снимок в подготовленное личное представление.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему календарное название приводит на кухню?</t>
+          <t xml:space="preserve">В народном описании Воздвижения появляются капустные хлопоты. Праздничное имя встречается с сезонной заготовкой семейного стола.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что исчезает, когда фотография остаётся без пояснения?</t>
+          <t xml:space="preserve">Подпись в альбоме сохраняет имя рядом с лицом. Несколько слов могут удержать связь поколений, которую само изображение уже не объясняет.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли восстановить дорогу письма по отметкам?</t>
+          <t xml:space="preserve">Почтовый адрес превращает конверт в маршрут. Имя получателя и название места помогают личному письму пройти через незнакомые руки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что заплата рассказывает о заботе?</t>
+          <t xml:space="preserve">Осенняя починка даёт одежде ещё один сезон. След ремонта показывает заботу о вещи и умение продолжить её службу вместо немедленной замены.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему одного визита могло быть недостаточно?</t>
+          <t xml:space="preserve">Сватовство не обязательно заканчивается первым визитом. Свадебная договорённость складывается по местному порядку, соединяя несколько действий и встреч.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что могли узнавать о будущей семье до свадьбы?</t>
+          <t xml:space="preserve">Перед браком знакомятся с другим хозяйством. Смотр дома показывает, что новая семейная связь касается повседневного устройства жизни.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как люди обозначали, что договорённость состоялась?</t>
+          <t xml:space="preserve">Рукобитье делает договорённость видимой. Жест становится частью местного свадебного порядка, по которому окружающие узнают о принятом решении.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему у большого обряда так много помощников?</t>
+          <t xml:space="preserve">Дружка, сваха и подруги выполняют разные свадебные роли. Общий праздник держится на людях, которым поручены конкретные действия.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сообщить о событии без общего чата?</t>
+          <t xml:space="preserve">Приглашение разносит свадебную новость по селу. Будущая встреча начинается раньше застолья — с личного обращения и принятого способа звать гостей.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется в общении подруг перед свадьбой?</t>
+          <t xml:space="preserve">Девичник собирает прежний круг перед переменой. Праздничная встреча сохраняет момент, когда отношения подруг получают новое продолжение.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему волосы становятся частью семейного обряда?</t>
+          <t xml:space="preserve">Невестина причёска меняется в ходе свадьбы. Волосы становятся видимым знаком перехода, который местная традиция оформляет определёнными действиями.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему на свадьбе можно услышать плач?</t>
+          <t xml:space="preserve">Свадебное причитание допускает печаль внутри праздника. Голос выражает переживание перемены, не отменяя радости общего события.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать различие без музыкального образования?</t>
+          <t xml:space="preserve">Причитание и песня по-разному организуют речь. В свадебной записи слышно, как человеческое переживание получает разные музыкальные формы.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вокруг небольшой украшенной вещи строится эпизод?</t>
+          <t xml:space="preserve">Свадебное деревце собирает вокруг себя действия участников. Небольшой предмет становится опорой местного обряда и последовательности встречи.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обычная полоска ткани становится памятной?</t>
+          <t xml:space="preserve">Лента невесты связана с прежним девичеством. Передача или смена украшения превращает личную вещь в знак перемены семейного положения.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто участвует в приготовлении и разделе хлеба?</t>
+          <t xml:space="preserve">Каравай включён в общее свадебное действие. Праздничная еда получает смысл через приготовление, встречу и участие конкретных людей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что поют не для сцены, а для события?</t>
+          <t xml:space="preserve">Каравайная песня сопровождает работу рук. Приготовление свадебного хлеба соединяет общий голос с последовательностью домашнего дела.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздник связан с разговорами о будущей семье?</t>
+          <t xml:space="preserve">Покров входит в народные свадебные ожидания осени. Праздничная дата хранит сезонную связь семейных надежд с завершением части хозяйственных работ.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему дорога между домами становится частью праздника?</t>
+          <t xml:space="preserve">Свадебный поезд делает переход видимым для деревни. Движение между домами связывает личное семейное событие с пространством всего поселения.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как трапеза выражает отношение к гостю?</t>
+          <t xml:space="preserve">Хлебом и солью встречают входящих в дом. Привычные продукты становятся частью принятия человека и открытого обращения хозяев к гостю.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что надевают после изменения причёски?</t>
+          <t xml:space="preserve">Свадебный убор меняет прежний вид невесты. Слои одежды оформляют переход, который окружающие считывают по местным правилам костюма.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в комнате не все места равноценны?</t>
+          <t xml:space="preserve">В красном углу собираются значимые домашние предметы. Порядок комнаты выделяет место, к которому обращаются в важных семейных обстоятельствах.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что может означать место человека на семейном пиру?</t>
+          <t xml:space="preserve">Рассадка делает отношения видимыми за столом. Место гостя связано с местным порядком встречи — близость к другому человеку не случайна.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как песня обращается к конкретному гостю?</t>
+          <t xml:space="preserve">Величальная песня называет достоинства человека. Праздничный голос обращает внимание собрания на того, кому адресованы слова.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему свадебная насмешка понятна участникам обряда?</t>
+          <t xml:space="preserve">Корильная песня включает шутку в свадебное общение. Её смысл зависит от ситуации и границ, которые признают участники конкретной традиции.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как обмен вещами укрепляет новые связи?</t>
+          <t xml:space="preserve">На свадебный дар отвечают отдариванием. Вещь проходит между людьми и поддерживает связь, которая не исчерпывается одной передачей подарка.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется название одного человека для разных родственников?</t>
+          <t xml:space="preserve">После свадьбы появляются новые названия родства. Свекровь, тёща и зять обозначают разные связи внутри расширившегося семейного круга.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие привычные действия становятся непривычными на новом месте?</t>
+          <t xml:space="preserve">Первое утро в новом доме продолжает свадебную перемену. За торжественным переходом начинается знакомство с повседневным порядком другой семьи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему нельзя собрать русскую свадьбу из случайных обычаев?</t>
+          <t xml:space="preserve">В Большебыкове свадьба имеет свой порядок. Местная запись сохраняет конкретные роли и действия, которые нельзя автоматически приписать всем русским сёлам.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как семейный обряд живёт в переселенческой среде?</t>
+          <t xml:space="preserve">Русская свадьба Томского Приобья живёт вдали от прежней родины. Запись позволяет увидеть местное продолжение семейной традиции в новом окружении.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что даёт запись людей, а не только пересказ обряда?</t>
+          <t xml:space="preserve">Северная свадьба Кебы сохраняется в голосах села. Имена исполнителей и обстоятельства записи возвращают обряду конкретное человеческое место.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему название традиции охватывает несколько поселений?</t>
+          <t xml:space="preserve">Локня и Ловать задают географию свадебных записей. Речная карта помогает различать местные варианты вместо одной собирательной церемонии.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что остаётся, если обряд перестали исполнять целиком?</t>
+          <t xml:space="preserve">Запись из Сланцевского района удерживает семейный обряд во времени. Слышимый голос связывает исследование традиции с конкретным исполнителем.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что изменилось в одежде и способе хранить память?</t>
+          <t xml:space="preserve">Городское свадебное фото выбирает новые позы и декорации. Семейное событие получает другой визуальный язык, сохраняя желание оставить память о встрече.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли рассказать о близких, не зная их точных слов?</t>
+          <t xml:space="preserve">Семейная история складывается из снимков, подписей и свидетельств. Отсутствующий разговор остаётся неизвестным — память сильнее без выдуманной цитаты.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему лаковая коробочка начинается не с дерева?</t>
+          <t xml:space="preserve">Бумага становится прочной федоскинской шкатулкой. Под живописью скрыта работа с основой — привычный материал получает неожиданную долговечную форму.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как глубина появляется на плоской крышке?</t>
+          <t xml:space="preserve">Блеск под федоскинской живописью меняет вид изображения. Свет проходит через художественные слои и становится частью мастерского замысла.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить несколько эпизодов в ладони?</t>
+          <t xml:space="preserve">На маленькой палехской крышке помещается большой сюжет. Масштаб миниатюры требует точности, чтобы фигуры и события оставались различимыми.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему похожие коробочки имеют разные авторские почерки?</t>
+          <t xml:space="preserve">Холуйская миниатюра сохраняет почерк местной школы. Общий вид ремесла не стирает различий в том, как мастера строят изображение.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как окружение помогает прочитать сюжет?</t>
+          <t xml:space="preserve">Мстёрский пейзаж окружает действие миниатюры. Маленькая поверхность вмещает пространство, в котором фигуры получают своё место и направление движения.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему маленькое украшение требует нескольких стадий?</t>
+          <t xml:space="preserve">Цвет ростовской финифти проходит через обжиг. Изображение возникает не одним движением кисти — огонь участвует в работе мастера.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металл выглядит лёгким кружевом?</t>
+          <t xml:space="preserve">Металлическая нить складывается в ажурную скань. Твёрдый материал выглядит лёгким благодаря изгибам, соединениям и оставленным просветам.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарь возвращает семью к ушедшим поколениям?</t>
+          <t xml:space="preserve">Память о родных собирает людей вместе. Обычай Дмитриева дня возвращает внимание к семейной связи, которая продолжается за пределами одной жизни.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему тёмная линия делает узор заметнее?</t>
+          <t xml:space="preserve">Великоустюжская чернь создаёт тёмный рисунок на серебре. Различие поверхностей помогает прочитать тонкую работу на небольшой металлической вещи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как имя святой входит в мир домашней работы?</t>
+          <t xml:space="preserve">Образ Параскевы Пятницы связан с женскими занятиями в народной традиции. Почитание получает местное выражение в отношении к труду и его ритму.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металлическая нить держится на ткани?</t>
+          <t xml:space="preserve">Блестящая нить торжокского шитья удерживается на ткани стежками. Под нарядной поверхностью находится точный порядок закрепления материала.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как убрать часть нитей и сохранить ткань?</t>
+          <t xml:space="preserve">В крестецкой строчке часть нитей убирают ради узора. Просветы становятся рисунком, а оставшиеся соединения удерживают ткань целой.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что соединяет крупные элементы узора?</t>
+          <t xml:space="preserve">Мелкая сетка елецкого кружева связывает крупные мотивы. Воздушный рисунок держится на деталях, которые легко пропустить при первом взгляде.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как один день объединяет работу и посиделки?</t>
+          <t xml:space="preserve">Кузьминки соединяют ремесленный труд с молодёжным общением. Праздничный день открывает другой порядок встречи внутри сезона вечерней работы.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли народное кружево рассказывать о машине?</t>
+          <t xml:space="preserve">Трактор появляется внутри кружевного узора. Народная техника принимает машинный сюжет — традиционное ремесло рассказывает о новой эпохе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как рисунок рассчитан на ношение?</t>
+          <t xml:space="preserve">Букет павловопосадского платка остаётся виден в складках. Композиция рассчитана на ношение: квадрат ткани работает в объёмном движении.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как материал соединяет лёгкость и укрытие?</t>
+          <t xml:space="preserve">Тонкая пуховая нить собирается в оренбургский платок. Лёгкость вещи связана с материалом и вязанием, которые можно рассмотреть вблизи.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как тяжёлый материал сохраняет тонкие детали?</t>
+          <t xml:space="preserve">Каслинское литьё передаёт тонкие детали в тяжёлом металле. Видимая лёгкость формы требует точной работы на разных этапах изготовления.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда рисунок попадает на тёмную основу?</t>
+          <t xml:space="preserve">Тёмный тагильский поднос становится цветочным полем. Роспись меняет восприятие металла, сохраняя форму вещи для повседневного использования.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить прочность вокруг тонких отверстий?</t>
+          <t xml:space="preserve">Шемогодский узор прорезан в бересте насквозь. Тонкие перемычки удерживают ажур целым — красота зависит от сохранённой прочности материала.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что здесь сделал мастер, а что выросло само?</t>
+          <t xml:space="preserve">Вятский кап приносит природный рисунок ещё до обработки. Мастер выбирает форму, в которой выросшая структура дерева становится видимой.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ажурная деталь складывается в цельную вещь?</t>
+          <t xml:space="preserve">Холмогорская резьба складывает ажур из маленьких просветов. Отдельная костяная деталь требует точного соединения с остальными частями вещи.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли узнать занятие человека по маленькой фигуре?</t>
+          <t xml:space="preserve">Тобольская миниатюра передаёт занятие человека в малом масштабе. Жест и рабочий предмет помогают прочитать сцену без длинного пояснения.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как округлый рельеф создаёт игру света?</t>
+          <t xml:space="preserve">Листья кудринской резьбы выступают над поверхностью дерева. Округлый рельеф меняет свет и тень, когда взгляд смещается вокруг вещи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рисунок должен учитывать ручку и край?</t>
+          <t xml:space="preserve">Роспись дулёвской чашки учитывает ручку и край. Цветок попадает на предмет, которым пользуются, — художественная композиция встречается с формой посуды.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается ёмкость и начинается фигурный декор?</t>
+          <t xml:space="preserve">Скопинский сосуд соединяет ёмкость с фигурным декором. Среди затейливых деталей остаются горло, ручка и рабочее устройство посуды.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем интересен промысел, о котором редко слышат?</t>
+          <t xml:space="preserve">Судогодская игрушка сохраняет местный почерк в маленькой форме. Сравнение близких вещей помогает заметить отличия, которые теряются за общим словом «промысел».</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как перестать воспринимать промысел как безымянное производство?</t>
+          <t xml:space="preserve">Подпись возвращает узору имя мастера. Народное ремесло состоит из труда конкретных людей — знакомый рисунок не возникает сам по себе.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что начинающий ещё не умеет делать автоматически?</t>
+          <t xml:space="preserve">Ученическая ошибка показывает ещё не освоенный приём. Сравнение работ делает видимым путь руки от первой попытки к уверенной точности мастера.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вечерний труд легче представить с другими людьми?</t>
+          <t xml:space="preserve">На посиделках трудятся и разговаривают вместе. Вечерняя работа становится местом общения, где передаются песни, рассказы и повседневный опыт.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему длинная шуба подходит не для всякого дела?</t>
+          <t xml:space="preserve">Полушубок оставляет больше свободы для работы, чем длинная верхняя одежда. Длина вещи связана с движением человека в зимнем хозяйстве.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как форма связана с работой на морозе?</t>
+          <t xml:space="preserve">Рукавица собирает пальцы в общем пространстве. Материал и следы износа помогают увидеть, как одежда служила рукам на морозе.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что наматывали на ногу перед выходом?</t>
+          <t xml:space="preserve">Онучи входят в обувной комплект раньше лаптя. Несколько слоёв работают вместе — повседневная обувь начинается с подготовки самой ноги.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном описании появляются сани?</t>
+          <t xml:space="preserve">В народных описаниях Введения появляется зимний выезд. Сани связывают праздничную встречу с дорогой, которая стала доступна по снегу.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рабочие сани выглядят иначе, чем прогулочные?</t>
+          <t xml:space="preserve">Розвальни расширяют место для хозяйственного груза. Рабочие сани отличаются от прогулочных потому, что служат другому содержимому и делу.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как уложить длинные поленья на короткую основу?</t>
+          <t xml:space="preserve">Дровни везут длинный груз на короткой основе. Укладка связывает устройство саней с будущим запасом тепла для дома.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему поленья не просто сваливают у стены?</t>
+          <t xml:space="preserve">Поленья складывают в поленницу, а не только собирают в кучу. Порядок укладки превращает множество отдельных кусков дерева в устроенный запас.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда устье печи закрывают?</t>
+          <t xml:space="preserve">Печной заслон закрывает устье большого очага. Небольшая съёмная деталь имеет своё место в устройстве, вокруг которого организован домашний труд.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему Юрьев день стал поговоркой?</t>
+          <t xml:space="preserve">Юрьев день остался в известной поговорке. Народное выражение хранит след исторической перемены, который требует отдельного объяснения событий.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно узнать о быте по углублению в стенке?</t>
+          <t xml:space="preserve">В стенке печи устроены маленькие ниши-печурки. Небольшая деталь показывает, как домашний быт использует пространство рядом с большим очагом.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как получить ещё одно место в небольшой избе?</t>
+          <t xml:space="preserve">Полати добавляют верхний ярус в небольшую избу. Домашнее пространство растёт по высоте, когда привычной площади пола недостаточно.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему кухонные вещи собраны в одном месте?</t>
+          <t xml:space="preserve">Бабий кут собирает предметы кухонной работы рядом. Часть комнаты организована последовательностью дел, которые каждый день повторяются в доме.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли судить о человеке по одной дорогой вещи?</t>
+          <t xml:space="preserve">Дорогая шуба на снимке видна сразу, жизнь её владельца — нет. Материал одежды даёт наблюдение, но достаток требует сведений о самом человеке.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие вещи хозяин держал отдельно от повседневных?</t>
+          <t xml:space="preserve">Шкатулка отделяет личные вещи от повседневного имущества. Внутренние отделения сохраняют порядок хранения, а подлинная опись возвращает содержимому имена.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как изображение и подпись работают вместе?</t>
+          <t xml:space="preserve">Лубок соединяет изображение с подписью. Рассказ разворачивается между видимым эпизодом и прочитанной строкой — взгляд и слово работают вместе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда текст звучит для всей комнаты?</t>
+          <t xml:space="preserve">Одну книгу читают вслух нескольким людям. Домашний текст становится общей встречей: слушатели разделяют время и голос читающего.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рассказчики не повторяют текст слово в слово?</t>
+          <t xml:space="preserve">Одна сказка живёт в разных записях. Рассказчики сохраняют узнаваемые события, но меняют слова и детали — устная традиция не повторяет страницу механически.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли назвать предмет, если о нём говорят обходно?</t>
+          <t xml:space="preserve">Загадка описывает знакомую вещь обходным путём. Образное сравнение скрывает предмет и одновременно даёт признаки, по которым его можно узнать.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем зимний Никола отличается от вешнего в народном быту?</t>
+          <t xml:space="preserve">Никола зимний и вешний входят в разные сезоны быта. Память об одном святом соединяется с разными хозяйственными обстоятельствами года.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему пословица понятна не в каждом случае?</t>
+          <t xml:space="preserve">Пословица раскрывается в подходящей жизненной ситуации. Короткая фраза переносит опыт, но её смысл нельзя одинаково приложить к любому случаю.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличают людей с одинаковыми именами?</t>
+          <t xml:space="preserve">Домашнее прозвище различает людей с одинаковыми именами. Внутри сообщества имя получает дополнительную семейную историю и местный смысл.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как праздничный репертуар отличается от лирического?</t>
+          <t xml:space="preserve">Зимний репертуар Лопатней продолжает годовой круг села. Назначение песни слышно через её связь с конкретным праздником и исполнением.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как записать умение, которое раньше показывали руками?</t>
+          <t xml:space="preserve">В семейном рецепте мера может быть записана «на глаз». Тетрадь сохраняет слова, а комментарий владельца помогает понять переданное руками умение.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли починить вещь, повторив её структуру?</t>
+          <t xml:space="preserve">Штопка восстанавливает переплетение внутри отверстия. Ремонт повторяет устройство ткани — повреждённая вещь получает ещё время службы.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что о дарителе рассказывает собственноручная отделка?</t>
+          <t xml:space="preserve">Собственноручная упаковка показывает заботу до открытия подарка. Внешняя отделка становится частью личного обращения к тому, кому предназначена вещь.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как простое повторение превращается в украшение комнаты?</t>
+          <t xml:space="preserve">Бумажная гирлянда растёт из повторённых элементов. Простая ручная работа собирает семью вокруг подготовки общего праздничного пространства.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем длинное украшение отличается от отдельной игрушки?</t>
+          <t xml:space="preserve">Стеклянные бусы проходят линией по нескольким веткам. Длинное украшение связывает части ёлки в общий рисунок, которого не даёт одна игрушка.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ребёнок превращается в персонажа?</t>
+          <t xml:space="preserve">Новогодняя маска помогает ребёнку войти в роль. Домашний праздник получает персонажа благодаря небольшой вещи, меняющей узнаваемое лицо.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что можно сшить из доступных домашних материалов?</t>
+          <t xml:space="preserve">Костюм для утренника собирают из доступных материалов. За детским праздничным образом остаётся семейная работа выбора, кроя и отделки.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как мастер сохраняет навык, меняя назначение изделия?</t>
+          <t xml:space="preserve">Современный мастер меняет назначение вещи и сохраняет старый приём. Традиция продолжается через освоенное действие, которому находится новая работа.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какие предметы расскажут о прожитом годе без длинной хроники?</t>
+          <t xml:space="preserve">Двенадцать вещей складываются в личный рассказ о годе. Выбранные истории соединяют сезоны, людей и труд без необходимости пересказывать всё подряд.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
